--- a/data/TTS/班別時間對照表/TTS_TD_當月班別時間對照表.xlsx
+++ b/data/TTS/班別時間對照表/TTS_TD_當月班別時間對照表.xlsx
@@ -745,115 +745,115 @@
     <t>10:00</t>
   </si>
   <si>
-    <t>8:30</t>
+    <t>08:30</t>
   </si>
   <si>
     <t>21:00</t>
   </si>
   <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>4:06</t>
-  </si>
-  <si>
-    <t>4:45</t>
-  </si>
-  <si>
-    <t>4:39</t>
-  </si>
-  <si>
-    <t>6:40</t>
-  </si>
-  <si>
-    <t>4:26</t>
-  </si>
-  <si>
-    <t>4:31</t>
-  </si>
-  <si>
-    <t>4:51</t>
-  </si>
-  <si>
-    <t>5:51</t>
-  </si>
-  <si>
-    <t>6:31</t>
-  </si>
-  <si>
-    <t>5:11</t>
-  </si>
-  <si>
-    <t>5:15</t>
-  </si>
-  <si>
-    <t>5:31</t>
-  </si>
-  <si>
-    <t>5:40</t>
-  </si>
-  <si>
-    <t>6:20</t>
-  </si>
-  <si>
-    <t>5:41</t>
-  </si>
-  <si>
-    <t>5:50</t>
-  </si>
-  <si>
-    <t>6:10</t>
-  </si>
-  <si>
-    <t>7:07</t>
-  </si>
-  <si>
-    <t>7:11</t>
-  </si>
-  <si>
-    <t>6:35</t>
-  </si>
-  <si>
-    <t>6:50</t>
-  </si>
-  <si>
-    <t>7:10</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>7:20</t>
-  </si>
-  <si>
-    <t>6:41</t>
-  </si>
-  <si>
-    <t>7:50</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>6:11</t>
-  </si>
-  <si>
-    <t>8:40</t>
-  </si>
-  <si>
-    <t>9:40</t>
-  </si>
-  <si>
-    <t>8:20</t>
-  </si>
-  <si>
-    <t>8:25</t>
-  </si>
-  <si>
-    <t>8:50</t>
-  </si>
-  <si>
-    <t>9:20</t>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>04:39</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>04:26</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:20</t>
   </si>
   <si>
     <t>10:10</t>
@@ -877,16 +877,16 @@
     <t>11:50</t>
   </si>
   <si>
-    <t>5:16</t>
-  </si>
-  <si>
-    <t>7:25</t>
-  </si>
-  <si>
-    <t>6:21</t>
-  </si>
-  <si>
-    <t>9:51</t>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>09:51</t>
   </si>
   <si>
     <t>10:30</t>
@@ -895,16 +895,16 @@
     <t>11:36</t>
   </si>
   <si>
-    <t>9:25</t>
-  </si>
-  <si>
-    <t>6:05</t>
-  </si>
-  <si>
-    <t>6:01</t>
-  </si>
-  <si>
-    <t>9:50</t>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>09:50</t>
   </si>
   <si>
     <t>10:25</t>
@@ -1135,16 +1135,16 @@
     <t>17:13</t>
   </si>
   <si>
-    <t>9:07</t>
-  </si>
-  <si>
-    <t>6:47</t>
-  </si>
-  <si>
-    <t>5:01</t>
-  </si>
-  <si>
-    <t>7:46</t>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>05:01</t>
+  </si>
+  <si>
+    <t>07:46</t>
   </si>
   <si>
     <t>10:15</t>
@@ -1153,22 +1153,22 @@
     <t>10:40</t>
   </si>
   <si>
-    <t>7:31</t>
-  </si>
-  <si>
-    <t>9:10</t>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>09:10</t>
   </si>
   <si>
     <t>11:43</t>
   </si>
   <si>
-    <t>9:15</t>
+    <t>09:15</t>
   </si>
   <si>
     <t>17:40</t>
   </si>
   <si>
-    <t>9:45</t>
+    <t>09:45</t>
   </si>
   <si>
     <t>11:23</t>
@@ -1198,10 +1198,10 @@
     <t>17:38</t>
   </si>
   <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t>6:00</t>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>06:00</t>
   </si>
   <si>
     <t>18:00</t>
@@ -1321,12 +1321,12 @@
     <t>20:40</t>
   </si>
   <si>
+    <t>14:21</t>
+  </si>
+  <si>
     <t>14:26</t>
   </si>
   <si>
-    <t>14:21</t>
-  </si>
-  <si>
     <t>21:05</t>
   </si>
   <si>
@@ -1570,220 +1570,220 @@
     <t>25:38</t>
   </si>
   <si>
-    <t>9:29</t>
-  </si>
-  <si>
-    <t>8:54</t>
-  </si>
-  <si>
-    <t>9:44</t>
-  </si>
-  <si>
-    <t>8:45</t>
-  </si>
-  <si>
-    <t>9:34</t>
-  </si>
-  <si>
-    <t>8:19</t>
-  </si>
-  <si>
-    <t>8:14</t>
-  </si>
-  <si>
-    <t>8:05</t>
-  </si>
-  <si>
-    <t>8:24</t>
-  </si>
-  <si>
-    <t>8:34</t>
-  </si>
-  <si>
-    <t>8:49</t>
-  </si>
-  <si>
-    <t>8:29</t>
-  </si>
-  <si>
-    <t>8:39</t>
-  </si>
-  <si>
-    <t>8:09</t>
-  </si>
-  <si>
-    <t>9:14</t>
-  </si>
-  <si>
-    <t>9:57</t>
-  </si>
-  <si>
-    <t>8:59</t>
-  </si>
-  <si>
-    <t>8:44</t>
-  </si>
-  <si>
-    <t>9:39</t>
-  </si>
-  <si>
-    <t>9:30</t>
-  </si>
-  <si>
-    <t>8:38</t>
-  </si>
-  <si>
-    <t>9:24</t>
-  </si>
-  <si>
-    <t>9:59</t>
-  </si>
-  <si>
-    <t>8:15</t>
-  </si>
-  <si>
-    <t>9:05</t>
-  </si>
-  <si>
-    <t>9:04</t>
-  </si>
-  <si>
-    <t>9:54</t>
-  </si>
-  <si>
-    <t>8:04</t>
-  </si>
-  <si>
-    <t>8:02</t>
-  </si>
-  <si>
-    <t>8:36</t>
-  </si>
-  <si>
-    <t>9:35</t>
-  </si>
-  <si>
-    <t>9:49</t>
-  </si>
-  <si>
-    <t>9:09</t>
-  </si>
-  <si>
-    <t>8:55</t>
-  </si>
-  <si>
-    <t>8:51</t>
-  </si>
-  <si>
-    <t>8:06</t>
-  </si>
-  <si>
-    <t>9:01</t>
-  </si>
-  <si>
-    <t>8:26</t>
-  </si>
-  <si>
-    <t>8:11</t>
-  </si>
-  <si>
-    <t>9:06</t>
-  </si>
-  <si>
-    <t>8:35</t>
-  </si>
-  <si>
-    <t>9:53</t>
-  </si>
-  <si>
-    <t>9:23</t>
-  </si>
-  <si>
-    <t>8:57</t>
-  </si>
-  <si>
-    <t>8:13</t>
-  </si>
-  <si>
-    <t>8:58</t>
-  </si>
-  <si>
-    <t>9:18</t>
-  </si>
-  <si>
-    <t>9:08</t>
-  </si>
-  <si>
-    <t>8:48</t>
-  </si>
-  <si>
-    <t>8:23</t>
-  </si>
-  <si>
-    <t>9:38</t>
-  </si>
-  <si>
-    <t>8:52</t>
-  </si>
-  <si>
-    <t>8:03</t>
-  </si>
-  <si>
-    <t>8:18</t>
-  </si>
-  <si>
-    <t>8:33</t>
-  </si>
-  <si>
-    <t>8:08</t>
-  </si>
-  <si>
-    <t>9:13</t>
-  </si>
-  <si>
-    <t>8:28</t>
-  </si>
-  <si>
-    <t>8:43</t>
-  </si>
-  <si>
-    <t>9:28</t>
-  </si>
-  <si>
-    <t>8:53</t>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t>9:55</t>
-  </si>
-  <si>
-    <t>9:37</t>
-  </si>
-  <si>
-    <t>9:03</t>
-  </si>
-  <si>
-    <t>9:48</t>
-  </si>
-  <si>
-    <t>9:58</t>
-  </si>
-  <si>
-    <t>9:26</t>
-  </si>
-  <si>
-    <t>9:19</t>
-  </si>
-  <si>
-    <t>9:33</t>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>08:39</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>09:57</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>08:02</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>09:49</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>08:51</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>08:08</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>09:48</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>09:33</t>
   </si>
   <si>
     <t>10/18(SUN), 10/23(FRI)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE)</t>
   </si>
   <si>
     <t>10/21(WED), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
@@ -1792,13 +1792,13 @@
     <t>10/14(WED)</t>
   </si>
   <si>
-    <t>10/8(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/9(FRI)</t>
+    <t>10/08(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/09(FRI), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/09(FRI)</t>
   </si>
   <si>
     <t>10/16(FRI), 10/19(MON), 10/23(FRI), 10/27(TUE)</t>
@@ -1807,10 +1807,10 @@
     <t>10/13(TUE), 10/15(THU)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/20(TUE), 10/21(WED), 10/27(TUE)</t>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/20(TUE), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/14(WED), 10/28(WED)</t>
@@ -1825,16 +1825,16 @@
     <t>10/26(MON)</t>
   </si>
   <si>
-    <t>10/5(MON)</t>
-  </si>
-  <si>
-    <t>10/9(FRI), 10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
+    <t>10/05(MON)</t>
+  </si>
+  <si>
+    <t>10/09(FRI), 10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/10(SAT), 10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/11(SUN), 10/18(SUN)</t>
+    <t>10/04(SUN), 10/11(SUN), 10/18(SUN)</t>
   </si>
   <si>
     <t>10/25(SUN)</t>
@@ -1843,13 +1843,13 @@
     <t>10/11(SUN)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/12(MON), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+    <t>10/04(SUN), 10/05(MON), 10/06(TUE), 10/07(WED), 10/12(MON), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
   </si>
   <si>
     <t>10/27(TUE)</t>
   </si>
   <si>
-    <t>10/9(FRI)</t>
+    <t>10/09(FRI)</t>
   </si>
   <si>
     <t>10/16(FRI), 10/30(FRI)</t>
@@ -1861,25 +1861,25 @@
     <t>10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/22(THU), 10/29(THU)</t>
   </si>
   <si>
-    <t>10/8(THU), 10/15(THU), 10/22(THU), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/12(MON)</t>
+    <t>10/08(THU), 10/15(THU), 10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/12(MON)</t>
   </si>
   <si>
     <t>10/19(MON)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/12(MON), 10/19(MON)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/11(SUN), 10/18(SUN), 10/25(SUN)</t>
+    <t>10/05(MON), 10/12(MON), 10/19(MON)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/11(SUN), 10/18(SUN), 10/25(SUN)</t>
   </si>
   <si>
     <t>10/10(SAT), 10/17(SAT), 10/31(SAT)</t>
@@ -1888,13 +1888,13 @@
     <t>10/24(SAT)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/11(SUN), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/19(MON), 10/21(WED), 10/25(SUN), 10/26(MON), 10/28(WED)</t>
+    <t>10/04(SUN), 10/05(MON), 10/06(TUE), 10/07(WED), 10/11(SUN), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/19(MON), 10/21(WED), 10/25(SUN), 10/26(MON), 10/28(WED)</t>
   </si>
   <si>
     <t>10/12(MON), 10/20(TUE), 10/27(TUE)</t>
   </si>
   <si>
-    <t>10/9(FRI), 10/16(FRI), 10/30(FRI)</t>
+    <t>10/09(FRI), 10/16(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
@@ -1906,94 +1906,94 @@
     <t>10/15(THU)</t>
   </si>
   <si>
-    <t>10/9(FRI), 10/10(SAT), 10/16(FRI), 10/17(SAT), 10/23(FRI), 10/24(SAT), 10/30(FRI), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/13(TUE), 10/20(TUE), 10/28(WED)</t>
+    <t>10/09(FRI), 10/10(SAT), 10/16(FRI), 10/17(SAT), 10/23(FRI), 10/24(SAT), 10/30(FRI), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/13(TUE), 10/20(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/14(WED), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
-    <t>10/6(TUE)</t>
-  </si>
-  <si>
-    <t>10/7(WED)</t>
+    <t>10/06(TUE)</t>
+  </si>
+  <si>
+    <t>10/07(WED)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/20(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/19(MON)</t>
+    <t>10/05(MON), 10/19(MON)</t>
   </si>
   <si>
     <t>10/12(MON)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/12(MON), 10/15(THU), 10/19(MON), 10/22(THU), 10/26(MON), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/12(MON), 10/19(MON), 10/26(MON)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/19(MON), 10/26(MON)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/10(SAT), 10/12(MON), 10/17(SAT), 10/19(MON), 10/24(SAT), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/20(TUE), 10/21(WED)</t>
+    <t>10/05(MON), 10/12(MON), 10/15(THU), 10/19(MON), 10/22(THU), 10/26(MON), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/12(MON), 10/19(MON), 10/26(MON)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/19(MON), 10/26(MON)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/10(SAT), 10/12(MON), 10/17(SAT), 10/19(MON), 10/24(SAT), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/20(TUE), 10/21(WED)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/20(TUE), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/15(THU), 10/20(TUE), 10/21(WED), 10/22(THU), 10/27(TUE), 10/28(WED), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/9(FRI), 10/11(SUN), 10/16(FRI), 10/18(SUN), 10/23(FRI), 10/25(SUN), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/18(SUN), 10/25(SUN)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/18(SUN)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+    <t>10/06(TUE), 10/07(WED), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/15(THU), 10/20(TUE), 10/21(WED), 10/22(THU), 10/27(TUE), 10/28(WED), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/09(FRI), 10/11(SUN), 10/16(FRI), 10/18(SUN), 10/23(FRI), 10/25(SUN), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/18(SUN), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/18(SUN)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
   </si>
   <si>
     <t>10/22(THU)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/9(FRI), 10/10(SAT), 10/12(MON), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/23(FRI), 10/29(THU), 10/30(FRI), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/26(MON)</t>
+    <t>10/05(MON), 10/09(FRI), 10/10(SAT), 10/12(MON), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/23(FRI), 10/29(THU), 10/30(FRI), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/26(MON)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED)</t>
   </si>
   <si>
     <t>10/28(WED)</t>
   </si>
   <si>
-    <t>10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/15(THU), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
+    <t>10/04(SUN), 10/15(THU), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/13(TUE)</t>
   </si>
   <si>
-    <t>10/7(WED), 10/21(WED), 10/28(WED)</t>
+    <t>10/07(WED), 10/21(WED), 10/28(WED)</t>
   </si>
   <si>
     <t>10/20(TUE)</t>
@@ -2002,19 +2002,19 @@
     <t>10/13(TUE), 10/14(WED), 10/27(TUE)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/20(TUE), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/15(THU), 10/17(SAT), 10/22(THU), 10/24(SAT), 10/29(THU), 10/31(SAT)</t>
+    <t>10/06(TUE), 10/07(WED), 10/20(TUE), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/15(THU), 10/17(SAT), 10/22(THU), 10/24(SAT), 10/29(THU), 10/31(SAT)</t>
   </si>
   <si>
     <t>10/15(THU), 10/29(THU)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/20(TUE), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/12(MON), 10/13(TUE), 10/14(WED), 10/19(MON), 10/27(TUE), 10/28(WED)</t>
+    <t>10/06(TUE), 10/20(TUE), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/12(MON), 10/13(TUE), 10/14(WED), 10/19(MON), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/14(WED), 10/15(THU), 10/28(WED), 10/29(THU)</t>
@@ -2023,7 +2023,7 @@
     <t>10/13(TUE), 10/14(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/8(THU), 10/22(THU)</t>
+    <t>10/08(THU), 10/22(THU)</t>
   </si>
   <si>
     <t>10/12(MON), 10/17(SAT), 10/31(SAT)</t>
@@ -2032,7 +2032,7 @@
     <t>10/17(SAT), 10/31(SAT)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/9(FRI), 10/16(FRI), 10/18(SUN), 10/30(FRI)</t>
+    <t>10/04(SUN), 10/09(FRI), 10/16(FRI), 10/18(SUN), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/23(FRI), 10/25(SUN)</t>
@@ -2047,55 +2047,55 @@
     <t>10/11(SUN), 10/25(SUN)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/15(THU), 10/21(WED), 10/22(THU), 10/28(WED), 10/29(THU)</t>
+    <t>10/06(TUE), 10/07(WED), 10/15(THU), 10/21(WED), 10/22(THU), 10/28(WED), 10/29(THU)</t>
   </si>
   <si>
     <t>10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/14(WED), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/24(SAT), 10/28(WED), 10/31(SAT)</t>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/14(WED), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/24(SAT), 10/28(WED), 10/31(SAT)</t>
   </si>
   <si>
     <t>10/12(MON), 10/13(TUE), 10/27(TUE)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/20(TUE), 10/21(WED)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/20(TUE), 10/21(WED)</t>
   </si>
   <si>
     <t>10/14(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/9(FRI), 10/30(FRI)</t>
+    <t>10/09(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/20(TUE), 10/21(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+    <t>10/06(TUE), 10/07(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
   </si>
   <si>
     <t>10/12(MON), 10/13(TUE), 10/19(MON)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/9(FRI), 10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/9(FRI), 10/14(WED), 10/16(FRI), 10/20(TUE), 10/21(WED), 10/28(WED), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/09(FRI), 10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/09(FRI), 10/14(WED), 10/16(FRI), 10/20(TUE), 10/21(WED), 10/28(WED), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/28(WED)</t>
@@ -2104,37 +2104,37 @@
     <t>10/22(THU), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/10(SAT), 10/14(WED), 10/23(FRI), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/15(THU), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/10(SAT), 10/13(TUE), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/28(WED), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/7(WED), 10/10(SAT), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/20(TUE), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/9(FRI), 10/11(SUN), 10/12(MON), 10/14(WED), 10/24(SAT), 10/25(SUN), 10/27(TUE)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/14(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/8(THU), 10/9(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/24(SAT)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/8(THU), 10/9(FRI), 10/11(SUN), 10/12(MON), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/25(SUN)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/5(MON), 10/7(WED), 10/9(FRI)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/11(SUN)</t>
+    <t>10/10(SAT), 10/14(WED), 10/23(FRI), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/15(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/10(SAT), 10/13(TUE), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/28(WED), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/07(WED), 10/10(SAT), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/20(TUE), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/09(FRI), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/09(FRI), 10/11(SUN), 10/12(MON), 10/14(WED), 10/24(SAT), 10/25(SUN), 10/27(TUE), 10/29(THU), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/14(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/08(THU), 10/09(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/24(SAT)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/05(MON), 10/06(TUE), 10/08(THU), 10/09(FRI), 10/11(SUN), 10/12(MON), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/05(MON), 10/07(WED), 10/09(FRI)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/11(SUN)</t>
   </si>
 </sst>
 </file>
@@ -2911,13 +2911,13 @@
         <v>250</v>
       </c>
       <c r="C25" t="s">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="D25" t="s">
         <v>525</v>
       </c>
       <c r="E25" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2928,13 +2928,13 @@
         <v>250</v>
       </c>
       <c r="C26" t="s">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="D26" t="s">
         <v>526</v>
       </c>
       <c r="E26" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3033,7 +3033,7 @@
         <v>305</v>
       </c>
       <c r="D32" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E32" t="s">
         <v>611</v>
@@ -3115,13 +3115,13 @@
         <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D37" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E37" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3132,13 +3132,13 @@
         <v>246</v>
       </c>
       <c r="C38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D38" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E38" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3200,13 +3200,13 @@
         <v>252</v>
       </c>
       <c r="C42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D42" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="E42" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3217,13 +3217,13 @@
         <v>252</v>
       </c>
       <c r="C43" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D43" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="E43" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3985,7 +3985,7 @@
         <v>410</v>
       </c>
       <c r="D88" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E88" t="s">
         <v>636</v>
@@ -4580,7 +4580,7 @@
         <v>333</v>
       </c>
       <c r="D123" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E123" t="s">
         <v>645</v>
@@ -4767,7 +4767,7 @@
         <v>333</v>
       </c>
       <c r="D134" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E134" t="s">
         <v>647</v>
@@ -4900,13 +4900,13 @@
         <v>282</v>
       </c>
       <c r="C142" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D142" t="s">
-        <v>521</v>
+        <v>272</v>
       </c>
       <c r="E142" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4917,13 +4917,13 @@
         <v>282</v>
       </c>
       <c r="C143" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D143" t="s">
-        <v>272</v>
+        <v>521</v>
       </c>
       <c r="E143" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5308,13 +5308,13 @@
         <v>294</v>
       </c>
       <c r="C166" t="s">
-        <v>410</v>
+        <v>335</v>
       </c>
       <c r="D166" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E166" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -5325,13 +5325,13 @@
         <v>294</v>
       </c>
       <c r="C167" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
       <c r="D167" t="s">
-        <v>382</v>
+        <v>242</v>
       </c>
       <c r="E167" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -5410,13 +5410,13 @@
         <v>273</v>
       </c>
       <c r="C172" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="D172" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="E172" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -5427,13 +5427,13 @@
         <v>273</v>
       </c>
       <c r="C173" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D173" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="E173" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -5529,13 +5529,13 @@
         <v>289</v>
       </c>
       <c r="C179" t="s">
-        <v>435</v>
+        <v>317</v>
       </c>
       <c r="D179" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="E179" t="s">
-        <v>654</v>
+        <v>610</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -5546,13 +5546,13 @@
         <v>289</v>
       </c>
       <c r="C180" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D180" t="s">
         <v>272</v>
       </c>
       <c r="E180" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -5563,13 +5563,13 @@
         <v>289</v>
       </c>
       <c r="C181" t="s">
-        <v>317</v>
+        <v>426</v>
       </c>
       <c r="D181" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="E181" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5580,13 +5580,13 @@
         <v>289</v>
       </c>
       <c r="C182" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D182" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E182" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -6056,13 +6056,13 @@
         <v>248</v>
       </c>
       <c r="C210" t="s">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="D210" t="s">
-        <v>272</v>
+        <v>556</v>
       </c>
       <c r="E210" t="s">
-        <v>607</v>
+        <v>649</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -6073,13 +6073,13 @@
         <v>248</v>
       </c>
       <c r="C211" t="s">
-        <v>305</v>
+        <v>402</v>
       </c>
       <c r="D211" t="s">
-        <v>556</v>
+        <v>272</v>
       </c>
       <c r="E211" t="s">
-        <v>649</v>
+        <v>607</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -6195,7 +6195,7 @@
         <v>445</v>
       </c>
       <c r="D218" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E218" t="s">
         <v>621</v>
@@ -6396,13 +6396,13 @@
         <v>309</v>
       </c>
       <c r="C230" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="D230" t="s">
-        <v>561</v>
+        <v>277</v>
       </c>
       <c r="E230" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -6413,13 +6413,13 @@
         <v>309</v>
       </c>
       <c r="C231" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="D231" t="s">
-        <v>277</v>
+        <v>561</v>
       </c>
       <c r="E231" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -6433,7 +6433,7 @@
         <v>437</v>
       </c>
       <c r="D232" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E232" t="s">
         <v>648</v>
@@ -6470,7 +6470,7 @@
         <v>272</v>
       </c>
       <c r="E234" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -6600,13 +6600,13 @@
         <v>312</v>
       </c>
       <c r="C242" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D242" t="s">
-        <v>564</v>
+        <v>276</v>
       </c>
       <c r="E242" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -6617,13 +6617,13 @@
         <v>312</v>
       </c>
       <c r="C243" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D243" t="s">
-        <v>276</v>
+        <v>564</v>
       </c>
       <c r="E243" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -6736,13 +6736,13 @@
         <v>316</v>
       </c>
       <c r="C250" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D250" t="s">
-        <v>272</v>
+        <v>566</v>
       </c>
       <c r="E250" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -6753,13 +6753,13 @@
         <v>316</v>
       </c>
       <c r="C251" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D251" t="s">
-        <v>566</v>
+        <v>272</v>
       </c>
       <c r="E251" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -7280,13 +7280,13 @@
         <v>317</v>
       </c>
       <c r="C282" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="D282" t="s">
-        <v>558</v>
+        <v>272</v>
       </c>
       <c r="E282" t="s">
-        <v>670</v>
+        <v>619</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -7297,13 +7297,13 @@
         <v>317</v>
       </c>
       <c r="C283" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="D283" t="s">
-        <v>272</v>
+        <v>558</v>
       </c>
       <c r="E283" t="s">
-        <v>619</v>
+        <v>670</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -8249,13 +8249,13 @@
         <v>354</v>
       </c>
       <c r="C339" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="D339" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="E339" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -8266,13 +8266,13 @@
         <v>354</v>
       </c>
       <c r="C340" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="D340" t="s">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="E340" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -8317,13 +8317,13 @@
         <v>356</v>
       </c>
       <c r="C343" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D343" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="E343" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -8334,13 +8334,13 @@
         <v>356</v>
       </c>
       <c r="C344" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="D344" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="E344" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -8385,13 +8385,13 @@
         <v>356</v>
       </c>
       <c r="C347" t="s">
-        <v>494</v>
+        <v>451</v>
       </c>
       <c r="D347" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="E347" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -8402,13 +8402,13 @@
         <v>356</v>
       </c>
       <c r="C348" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
       <c r="D348" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="E348" t="s">
-        <v>608</v>
+        <v>649</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -9014,13 +9014,13 @@
         <v>312</v>
       </c>
       <c r="C384" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D384" t="s">
-        <v>521</v>
+        <v>561</v>
       </c>
       <c r="E384" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -9031,13 +9031,13 @@
         <v>312</v>
       </c>
       <c r="C385" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D385" t="s">
-        <v>561</v>
+        <v>521</v>
       </c>
       <c r="E385" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -9473,13 +9473,13 @@
         <v>350</v>
       </c>
       <c r="C411" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="D411" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="E411" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -9490,13 +9490,13 @@
         <v>350</v>
       </c>
       <c r="C412" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="D412" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="E412" t="s">
-        <v>610</v>
+        <v>658</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -9507,13 +9507,13 @@
         <v>350</v>
       </c>
       <c r="C413" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D413" t="s">
-        <v>565</v>
+        <v>534</v>
       </c>
       <c r="E413" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -9524,13 +9524,13 @@
         <v>350</v>
       </c>
       <c r="C414" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D414" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="E414" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -10000,13 +10000,13 @@
         <v>318</v>
       </c>
       <c r="C442" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="D442" t="s">
-        <v>566</v>
+        <v>274</v>
       </c>
       <c r="E442" t="s">
-        <v>693</v>
+        <v>637</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -10017,13 +10017,13 @@
         <v>318</v>
       </c>
       <c r="C443" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
       <c r="D443" t="s">
-        <v>274</v>
+        <v>566</v>
       </c>
       <c r="E443" t="s">
-        <v>637</v>
+        <v>693</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -10938,7 +10938,7 @@
         <v>445</v>
       </c>
       <c r="D497" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E497" t="s">
         <v>613</v>
